--- a/output/laminas_comunales/comunal_i_peringr_median_a_2022_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2022_o_higgins.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>29.46</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>28.89</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>27.57</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>26.15</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>24.47</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>24.17</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>23.8</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>23.14</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>22.38</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>21.93</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>20.43</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>19.93</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>19.78</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>19.71</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>19.57</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>19.43</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>19.38</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>19.09</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>18.91</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>18.48</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>17.67</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>17.58</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>17.23</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>16.7</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>16.26</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>16.01</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>15.34</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>15.28</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>15.28</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>14.05</v>
       </c>
-      <c r="F31" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>13.23</v>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -799,9 +701,6 @@
       <c r="B33">
         <v>12.7</v>
       </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -811,9 +710,6 @@
       </c>
       <c r="B34">
         <v>9.15</v>
-      </c>
-      <c r="F34" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringr_median_a_2022_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2022_o_higgins.xlsx
@@ -391,6 +391,15 @@
       <c r="B2">
         <v>29.46</v>
       </c>
+      <c r="C2">
+        <v>28.85</v>
+      </c>
+      <c r="D2">
+        <v>0.6099999999999994</v>
+      </c>
+      <c r="E2">
+        <v>2.114384748700182</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -401,6 +410,15 @@
       <c r="B3">
         <v>28.89</v>
       </c>
+      <c r="C3">
+        <v>29.17</v>
+      </c>
+      <c r="D3">
+        <v>-0.2800000000000011</v>
+      </c>
+      <c r="E3">
+        <v>-0.9598902982516311</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -411,6 +429,15 @@
       <c r="B4">
         <v>27.57</v>
       </c>
+      <c r="C4">
+        <v>26.98</v>
+      </c>
+      <c r="D4">
+        <v>0.5899999999999999</v>
+      </c>
+      <c r="E4">
+        <v>2.186805040770934</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -421,6 +448,15 @@
       <c r="B5">
         <v>26.15</v>
       </c>
+      <c r="C5">
+        <v>27.8</v>
+      </c>
+      <c r="D5">
+        <v>-1.650000000000002</v>
+      </c>
+      <c r="E5">
+        <v>-5.935251798561159</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -431,6 +467,15 @@
       <c r="B6">
         <v>24.47</v>
       </c>
+      <c r="C6">
+        <v>23.63</v>
+      </c>
+      <c r="D6">
+        <v>0.8399999999999999</v>
+      </c>
+      <c r="E6">
+        <v>3.554803216250524</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -441,6 +486,15 @@
       <c r="B7">
         <v>24.17</v>
       </c>
+      <c r="C7">
+        <v>24.47</v>
+      </c>
+      <c r="D7">
+        <v>-0.2999999999999972</v>
+      </c>
+      <c r="E7">
+        <v>-1.225991009399252</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -451,6 +505,15 @@
       <c r="B8">
         <v>23.8</v>
       </c>
+      <c r="C8">
+        <v>24.47</v>
+      </c>
+      <c r="D8">
+        <v>-0.6699999999999982</v>
+      </c>
+      <c r="E8">
+        <v>-2.738046587658349</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -461,6 +524,15 @@
       <c r="B9">
         <v>23.14</v>
       </c>
+      <c r="C9">
+        <v>23.26</v>
+      </c>
+      <c r="D9">
+        <v>-0.120000000000001</v>
+      </c>
+      <c r="E9">
+        <v>-0.5159071367153989</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -471,6 +543,15 @@
       <c r="B10">
         <v>22.38</v>
       </c>
+      <c r="C10">
+        <v>24.66</v>
+      </c>
+      <c r="D10">
+        <v>-2.280000000000001</v>
+      </c>
+      <c r="E10">
+        <v>-9.245742092457421</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -481,6 +562,15 @@
       <c r="B11">
         <v>21.93</v>
       </c>
+      <c r="C11">
+        <v>22.62</v>
+      </c>
+      <c r="D11">
+        <v>-0.6900000000000013</v>
+      </c>
+      <c r="E11">
+        <v>-3.05039787798409</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -491,6 +581,15 @@
       <c r="B12">
         <v>20.43</v>
       </c>
+      <c r="C12">
+        <v>22.05</v>
+      </c>
+      <c r="D12">
+        <v>-1.620000000000001</v>
+      </c>
+      <c r="E12">
+        <v>-7.346938775510203</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -501,6 +600,15 @@
       <c r="B13">
         <v>19.93</v>
       </c>
+      <c r="C13">
+        <v>20.43</v>
+      </c>
+      <c r="D13">
+        <v>-0.5</v>
+      </c>
+      <c r="E13">
+        <v>-2.447381302006857</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -511,6 +619,15 @@
       <c r="B14">
         <v>19.78</v>
       </c>
+      <c r="C14">
+        <v>20.09</v>
+      </c>
+      <c r="D14">
+        <v>-0.3099999999999987</v>
+      </c>
+      <c r="E14">
+        <v>-1.543056246888996</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -521,6 +638,15 @@
       <c r="B15">
         <v>19.71</v>
       </c>
+      <c r="C15">
+        <v>21.71</v>
+      </c>
+      <c r="D15">
+        <v>-2</v>
+      </c>
+      <c r="E15">
+        <v>-9.212344541685857</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -531,6 +657,15 @@
       <c r="B16">
         <v>19.57</v>
       </c>
+      <c r="C16">
+        <v>20.23</v>
+      </c>
+      <c r="D16">
+        <v>-0.6600000000000001</v>
+      </c>
+      <c r="E16">
+        <v>-3.262481463173506</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -541,6 +676,15 @@
       <c r="B17">
         <v>19.43</v>
       </c>
+      <c r="C17">
+        <v>20.38</v>
+      </c>
+      <c r="D17">
+        <v>-0.9499999999999993</v>
+      </c>
+      <c r="E17">
+        <v>-4.661432777232577</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -551,6 +695,15 @@
       <c r="B18">
         <v>19.38</v>
       </c>
+      <c r="C18">
+        <v>20.85</v>
+      </c>
+      <c r="D18">
+        <v>-1.470000000000002</v>
+      </c>
+      <c r="E18">
+        <v>-7.050359712230225</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -561,6 +714,15 @@
       <c r="B19">
         <v>19.09</v>
       </c>
+      <c r="C19">
+        <v>20.11</v>
+      </c>
+      <c r="D19">
+        <v>-1.02</v>
+      </c>
+      <c r="E19">
+        <v>-5.072103431128793</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -571,6 +733,15 @@
       <c r="B20">
         <v>18.91</v>
       </c>
+      <c r="C20">
+        <v>20.72</v>
+      </c>
+      <c r="D20">
+        <v>-1.809999999999999</v>
+      </c>
+      <c r="E20">
+        <v>-8.735521235521226</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -581,6 +752,15 @@
       <c r="B21">
         <v>18.48</v>
       </c>
+      <c r="C21">
+        <v>20.73</v>
+      </c>
+      <c r="D21">
+        <v>-2.25</v>
+      </c>
+      <c r="E21">
+        <v>-10.85383502170767</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -591,6 +771,15 @@
       <c r="B22">
         <v>17.67</v>
       </c>
+      <c r="C22">
+        <v>18.79</v>
+      </c>
+      <c r="D22">
+        <v>-1.119999999999997</v>
+      </c>
+      <c r="E22">
+        <v>-5.960617349654063</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -601,25 +790,52 @@
       <c r="B23">
         <v>17.58</v>
       </c>
+      <c r="C23">
+        <v>18.96</v>
+      </c>
+      <c r="D23">
+        <v>-1.380000000000003</v>
+      </c>
+      <c r="E23">
+        <v>-7.278481012658244</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B24">
-        <v>17.23</v>
+        <v>17.36</v>
+      </c>
+      <c r="C24">
+        <v>18.52</v>
+      </c>
+      <c r="D24">
+        <v>-1.16</v>
+      </c>
+      <c r="E24">
+        <v>-6.263498920086397</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marchihue</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="B25">
-        <v>16.7</v>
+        <v>17.23</v>
+      </c>
+      <c r="C25">
+        <v>19.65</v>
+      </c>
+      <c r="D25">
+        <v>-2.419999999999998</v>
+      </c>
+      <c r="E25">
+        <v>-12.31552162849871</v>
       </c>
     </row>
     <row r="26">
@@ -631,6 +847,15 @@
       <c r="B26">
         <v>16.26</v>
       </c>
+      <c r="C26">
+        <v>18.77</v>
+      </c>
+      <c r="D26">
+        <v>-2.509999999999998</v>
+      </c>
+      <c r="E26">
+        <v>-13.37240277037825</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -641,6 +866,15 @@
       <c r="B27">
         <v>16.01</v>
       </c>
+      <c r="C27">
+        <v>16.65</v>
+      </c>
+      <c r="D27">
+        <v>-0.639999999999997</v>
+      </c>
+      <c r="E27">
+        <v>-3.84384384384383</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -651,6 +885,15 @@
       <c r="B28">
         <v>15.34</v>
       </c>
+      <c r="C28">
+        <v>17.56</v>
+      </c>
+      <c r="D28">
+        <v>-2.219999999999999</v>
+      </c>
+      <c r="E28">
+        <v>-12.64236902050113</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -661,6 +904,15 @@
       <c r="B29">
         <v>15.28</v>
       </c>
+      <c r="C29">
+        <v>16.9</v>
+      </c>
+      <c r="D29">
+        <v>-1.619999999999999</v>
+      </c>
+      <c r="E29">
+        <v>-9.585798816568047</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -671,6 +923,15 @@
       <c r="B30">
         <v>15.28</v>
       </c>
+      <c r="C30">
+        <v>16.94</v>
+      </c>
+      <c r="D30">
+        <v>-1.660000000000002</v>
+      </c>
+      <c r="E30">
+        <v>-9.799291617473449</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -681,6 +942,15 @@
       <c r="B31">
         <v>14.05</v>
       </c>
+      <c r="C31">
+        <v>13.93</v>
+      </c>
+      <c r="D31">
+        <v>0.120000000000001</v>
+      </c>
+      <c r="E31">
+        <v>0.8614501076812608</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -691,6 +961,15 @@
       <c r="B32">
         <v>13.23</v>
       </c>
+      <c r="C32">
+        <v>14.8</v>
+      </c>
+      <c r="D32">
+        <v>-1.57</v>
+      </c>
+      <c r="E32">
+        <v>-10.60810810810811</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -701,6 +980,15 @@
       <c r="B33">
         <v>12.7</v>
       </c>
+      <c r="C33">
+        <v>13.4</v>
+      </c>
+      <c r="D33">
+        <v>-0.7000000000000011</v>
+      </c>
+      <c r="E33">
+        <v>-5.223880597014929</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -710,6 +998,15 @@
       </c>
       <c r="B34">
         <v>9.15</v>
+      </c>
+      <c r="C34">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="D34">
+        <v>-0.4699999999999989</v>
+      </c>
+      <c r="E34">
+        <v>-4.885654885654878</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -867,200 +1164,190 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marchihue</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="B15">
-        <v>16.7</v>
+        <v>17.58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="B16">
-        <v>17.58</v>
+        <v>23.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="B17">
-        <v>23.14</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="B18">
-        <v>12.7</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="B19">
-        <v>15.34</v>
+        <v>24.47</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="B20">
-        <v>24.47</v>
+        <v>29.46</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="B21">
-        <v>29.46</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="B22">
-        <v>19.78</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="B23">
-        <v>19.57</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="B24">
-        <v>23.8</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="B25">
-        <v>17.23</v>
+        <v>22.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="B26">
-        <v>22.38</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="B27">
-        <v>19.71</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="B28">
-        <v>19.93</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="B29">
-        <v>13.23</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="B30">
-        <v>19.38</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="B31">
-        <v>18.48</v>
+        <v>17.67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="B32">
-        <v>17.67</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="B33">
-        <v>18.91</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B34">
         <v>20.43</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_peringr_median_a_2022_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2022_o_higgins.xlsx
@@ -1016,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1025,330 +1025,236 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Chépica</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>28.89</v>
+          <t>Marchigüe</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>24.17</v>
+          <t>Codegua</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Codegua</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>16.01</v>
+          <t>Coinco</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coinco</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>15.28</v>
+          <t>Coltauco</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coltauco</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>19.43</v>
+          <t>Graneros</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Doñihue</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>14.05</v>
+          <t>Malloa</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Graneros</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>19.09</v>
+          <t>Peumo</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>La Estrella</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>15.28</v>
+          <t>Pichidegua</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>26.15</v>
+          <t>Rancagua</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Litueche</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>16.26</v>
+          <t>Requínoa</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lolol</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>27.57</v>
+          <t>Mostazal</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machalí</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>9.15</v>
+          <t>San Vicente</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Malloa</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>21.93</v>
+          <t>Nancagua</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Mostazal</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>17.58</v>
+          <t>Peralillo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Nancagua</t>
-        </is>
-      </c>
-      <c r="B16">
-        <v>23.14</v>
+          <t>Placilla</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Navidad</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>12.7</v>
+          <t>Pumanque</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Olivar</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>15.34</v>
+          <t>Paredones</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Palmilla</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>24.47</v>
+          <t>Pichilemu</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paredones</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>29.46</v>
+          <t>Litueche</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Peralillo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>19.78</v>
+          <t>Navidad</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Peumo</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>19.57</v>
+          <t>La Estrella</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
-        </is>
-      </c>
-      <c r="B23">
-        <v>23.8</v>
+          <t>Doñihue</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>17.23</v>
+          <t>Olivar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Placilla</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>22.38</v>
+          <t>Rengo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pumanque</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>19.71</v>
+          <t>Santa Cruz</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>19.93</v>
+          <t>Palmilla</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rancagua</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>13.23</v>
+          <t>Quinta de Tilcoco</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Rengo</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>19.38</v>
+          <t>Machalí</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Requínoa</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>18.48</v>
+          <t>Las Cabras</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Fernando</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>17.67</v>
+          <t>Chimbarongo</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>San Vicente</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>18.91</v>
+          <t>Lolol</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>20.43</v>
+          <t>Chépica</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>San Fernando</t>
+        </is>
       </c>
     </row>
   </sheetData>
